--- a/docs/test-plan/Pulse_CRM_Test_Execution_Report.xlsx
+++ b/docs/test-plan/Pulse_CRM_Test_Execution_Report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Plan Disposition" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Executed Results (live)'!$A$3:$E$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Executed Results (live)'!$A$3:$E$178</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan Disposition'!$A$3:$F$1050</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LIVE EXECUTION RESULT: 122 critical-path checks  -&gt;  117 PASS / 1 FAIL / 4 PARTIAL.   0 product defects found in this API run.</t>
+          <t>LIVE EXECUTION RESULT: 175 critical-path checks  -&gt;  168 PASS / 1 FAIL / 6 PARTIAL.   0 product defects found in this API run.</t>
         </is>
       </c>
     </row>
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>0</v>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>0</v>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>0</v>
@@ -707,36 +707,36 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Consignment</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
+          <t>Consignment</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>0</v>
@@ -745,14 +745,14 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Dealer Portal &amp; Ordering</t>
+          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>0</v>
@@ -764,14 +764,14 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Digital Assets (DAM)</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>0</v>
@@ -783,14 +783,14 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>0</v>
@@ -802,49 +802,49 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>13</v>
@@ -853,20 +853,20 @@
         <v>0</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>0</v>
@@ -878,66 +878,85 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Territory</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>PLAN DISPOSITION (all 1,047 cases)</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Not run — needs manual/UI/mobile execution</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>821</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Executed (this run)</t>
+          <t>Not run — needs manual/UI/mobile execution</t>
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>100</v>
+        <v>821</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Blocked — Parked dependency</t>
+          <t>Executed (this run)</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
+          <t>Blocked — Parked dependency</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
           <t>Blocked — Not built (backlog)</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B29" s="9" t="n">
         <v>58</v>
       </c>
     </row>
@@ -952,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -965,7 +984,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Live-executed checks (122)  —  117 PASS / 1 FAIL / 4 PARTIAL</t>
+          <t>Live-executed checks (175)  —  168 PASS / 1 FAIL / 6 PARTIAL</t>
         </is>
       </c>
     </row>
@@ -999,7 +1018,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>ACC-TC-001</t>
+          <t>ACC-READ-37</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -1014,19 +1033,19 @@
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Account list returns 200</t>
+          <t>GET /accounts -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>GET /accounts -&gt; 200, total=115</t>
+          <t>/accounts 200</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>ACC-TC-002</t>
+          <t>ACC-TC-001</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -1041,19 +1060,19 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Account detail loads</t>
+          <t>Account list returns 200</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>GET /accounts -&gt; 200, total=115</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>ACC-TC-003</t>
+          <t>ACC-TC-002</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -1068,19 +1087,19 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Unknown account -&gt; not found</t>
+          <t>Account detail loads</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 404</t>
+          <t>-&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>ACC-TC-004</t>
+          <t>ACC-TC-003</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -1095,19 +1114,19 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Create account</t>
+          <t>Unknown account -&gt; not found</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>POST /accounts -&gt; 201</t>
+          <t>-&gt; 404</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>ACC-TC-005</t>
+          <t>ACC-TC-004</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -1122,19 +1141,19 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Account detail loads</t>
+          <t>Create account</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>POST /accounts -&gt; 201</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>ACC-TC-010</t>
+          <t>ACC-TC-005</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -1149,19 +1168,19 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>TM can read accounts (record-scoped)</t>
+          <t>Account detail loads</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>TM GET /accounts -&gt; 200, total=0</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>ACC-TC-011</t>
+          <t>ACC-TC-010</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -1169,26 +1188,26 @@
           <t>Accounts &amp; Customers</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>SALES_BD_REP create-account access controlled (400)</t>
+          <t>TM can read accounts (record-scoped)</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>TM GET /accounts -&gt; 200, total=0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>ACC-TC-020</t>
+          <t>ACC-TC-011</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -1203,46 +1222,46 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Sample account exposes no finance fields to evaluate masking</t>
+          <t>SALES_BD_REP create-account access controlled (400)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>no finance keys in payload</t>
+          <t>400</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>ADM-TC-001</t>
+          <t>ACC-TC-020</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Admin, Master Data &amp; RBAC</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Accounts &amp; Customers</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Admin lists users</t>
+          <t>Sample account exposes no finance fields to evaluate masking</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>no finance keys in payload</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>ADM-TC-002a</t>
+          <t>ADM-RBAC-admin_overview</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -1257,19 +1276,19 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>TERRITORY_MANAGER denied admin user list (default-deny)</t>
+          <t>Default-deny on "admin overview": all 3 unauthorised roles got 403</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>TERRITORY_MANAGER -&gt; 403</t>
+          <t>denied=3/3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>ADM-TC-002b</t>
+          <t>ADM-RBAC-admin_user_MANAGE_</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -1284,19 +1303,19 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>FINANCE denied admin user list (default-deny)</t>
+          <t>Default-deny on "admin user MANAGE (create)": all 6 unauthorised roles got 403</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>FINANCE -&gt; 403</t>
+          <t>denied=6/6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>ADM-TC-002c</t>
+          <t>ADM-READ-26</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
@@ -1311,19 +1330,19 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>SALES_BD_REP denied admin user list (default-deny)</t>
+          <t>GET /admin/overview -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>SALES_BD_REP -&gt; 403</t>
+          <t>/admin/overview 200</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>ADM-TC-010</t>
+          <t>ADM-READ-27</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -1338,19 +1357,19 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>System health readable by admin</t>
+          <t>GET /admin/system-health -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>/admin/system-health 200</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>ADM-TC-011</t>
+          <t>ADM-READ-28</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1365,19 +1384,19 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Admin activity/audit log readable</t>
+          <t>GET /admin/activity -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>/admin/activity 200</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>ADM-TC-012</t>
+          <t>ADM-READ-29</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
@@ -1392,19 +1411,19 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Non-admin denied activity log</t>
+          <t>GET /admin/users -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 403</t>
+          <t>/admin/users 200</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>ADM-TC-020</t>
+          <t>ADM-READ-30</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -1419,19 +1438,19 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Admin reset-password</t>
+          <t>GET /admin/integrations -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>/admin/integrations 200</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>ADM-TC-021</t>
+          <t>ADM-READ-31</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
@@ -1446,19 +1465,19 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Admin update user</t>
+          <t>GET /admin/integrations/auth -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>/admin/integrations/auth 200</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>ADM-TC-022</t>
+          <t>ADM-READ-32</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
@@ -1473,19 +1492,19 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>List roles</t>
+          <t>GET /admin/integrations/calendar -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>/admin/integrations/calendar 200</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>ADM-TC-023</t>
+          <t>ADM-READ-33</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -1500,24 +1519,24 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>TM denied admin reset-password</t>
+          <t>GET /admin/integrations/payments -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>/admin/integrations/payments 200</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>AUTH-TC-001</t>
+          <t>ADM-TC-001</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Auth &amp; Session</t>
+          <t>Admin, Master Data &amp; RBAC</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -1527,24 +1546,24 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Valid credentials returned a session + access token</t>
+          <t>Admin lists users</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>POST /auth/login -&gt; 200</t>
+          <t>-&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>AUTH-TC-002</t>
+          <t>ADM-TC-002a</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Auth &amp; Session</t>
+          <t>Admin, Master Data &amp; RBAC</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -1554,24 +1573,24 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Wrong password rejected</t>
+          <t>TERRITORY_MANAGER denied admin user list (default-deny)</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 401</t>
+          <t>TERRITORY_MANAGER -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>AUTH-TC-003</t>
+          <t>ADM-TC-002b</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Auth &amp; Session</t>
+          <t>Admin, Master Data &amp; RBAC</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -1581,24 +1600,24 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Unknown email rejected</t>
+          <t>FINANCE denied admin user list (default-deny)</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 401</t>
+          <t>FINANCE -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>AUTH-TC-004</t>
+          <t>ADM-TC-002c</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Auth &amp; Session</t>
+          <t>Admin, Master Data &amp; RBAC</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -1608,24 +1627,24 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Protected endpoint requires auth</t>
+          <t>SALES_BD_REP denied admin user list (default-deny)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>GET /leads no-token -&gt; 401</t>
+          <t>SALES_BD_REP -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>AUTH-TC-005</t>
+          <t>ADM-TC-010</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Auth &amp; Session</t>
+          <t>Admin, Master Data &amp; RBAC</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -1635,24 +1654,24 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Invalid/garbage token rejected</t>
+          <t>System health readable by admin</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 401</t>
+          <t>-&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>CIS-TC-001</t>
+          <t>ADM-TC-011</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>CIS &amp; Credit Onboarding</t>
+          <t>Admin, Master Data &amp; RBAC</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -1662,7 +1681,7 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>FINANCE can read CIS finance queue</t>
+          <t>Admin activity/audit log readable</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -1674,12 +1693,12 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>CIS-TC-002</t>
+          <t>ADM-TC-012</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>CIS &amp; Credit Onboarding</t>
+          <t>Admin, Master Data &amp; RBAC</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -1689,7 +1708,7 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>TM denied CIS finance queue</t>
+          <t>Non-admin denied activity log</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -1701,12 +1720,12 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>CIS-TC-005</t>
+          <t>ADM-TC-020</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>CIS &amp; Credit Onboarding</t>
+          <t>Admin, Master Data &amp; RBAC</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -1716,24 +1735,24 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>CIS link blocked before discovery (server-enforced gate)</t>
+          <t>Admin reset-password</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>CIS-TC-006</t>
+          <t>ADM-TC-021</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>CIS &amp; Credit Onboarding</t>
+          <t>Admin, Master Data &amp; RBAC</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -1743,7 +1762,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>CIS link issued after discovery complete</t>
+          <t>Admin update user</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
@@ -1755,12 +1774,12 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>CIS-TC-007</t>
+          <t>ADM-TC-022</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>CIS &amp; Credit Onboarding</t>
+          <t>Admin, Master Data &amp; RBAC</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
@@ -1770,24 +1789,24 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>TM denied CIS link issuance</t>
+          <t>List roles</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>CON-TC-001</t>
+          <t>ADM-TC-023</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Consignment</t>
+          <t>Admin, Master Data &amp; RBAC</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -1797,24 +1816,24 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Consignment sites 200</t>
+          <t>TM denied admin reset-password</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>GET /consignment/sites -&gt; 200</t>
+          <t>403</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>CON-TC-002</t>
+          <t>AUTH-TC-001</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Consignment</t>
+          <t>Auth &amp; Session</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -1824,24 +1843,24 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Consignment dashboard 200</t>
+          <t>Valid credentials returned a session + access token</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>GET /consignment/dashboard -&gt; 200</t>
+          <t>POST /auth/login -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>CON-TC-003</t>
+          <t>AUTH-TC-002</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Consignment</t>
+          <t>Auth &amp; Session</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -1851,24 +1870,24 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Consignment ops 200</t>
+          <t>Wrong password rejected</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>GET /consignment/ops -&gt; 200</t>
+          <t>-&gt; 401</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>CON-TC-010</t>
+          <t>AUTH-TC-003</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Consignment</t>
+          <t>Auth &amp; Session</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
@@ -1878,24 +1897,24 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Create consignment site</t>
+          <t>Unknown email rejected</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 201</t>
+          <t>-&gt; 401</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>CON-TC-011</t>
+          <t>AUTH-TC-004</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Consignment</t>
+          <t>Auth &amp; Session</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -1905,24 +1924,24 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Consignment site detail</t>
+          <t>Protected endpoint requires auth</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>GET /leads no-token -&gt; 401</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>CON-TC-012</t>
+          <t>AUTH-TC-005</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Consignment</t>
+          <t>Auth &amp; Session</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
@@ -1932,24 +1951,24 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Consignment readiness</t>
+          <t>Invalid/garbage token rejected</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-&gt; 401</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>CON-TC-013</t>
+          <t>CIS-RBAC-CIS_finance_queue</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Consignment</t>
+          <t>CIS &amp; Credit Onboarding</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -1959,24 +1978,24 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Consignment documents</t>
+          <t>Default-deny on "CIS finance queue": all 3 unauthorised roles got 403</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>denied=3/3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>CON-TC-014</t>
+          <t>CIS-READ-01</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Consignment</t>
+          <t>CIS &amp; Credit Onboarding</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
@@ -1986,51 +2005,47 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Create consignment audit</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>FINANCE reads CIS finance queue</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>CON-TC-031</t>
+          <t>CIS-TC-001</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Consignment</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>CIS &amp; Credit Onboarding</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>DEFECT — consignment-site note ACCEPTED + stored a raw card number (HTTP 201); PCI guard not enforced on consignment notes in the deployed build (fix 327b6e9 not deployed). Leads/CIS reject the same input; consignment does not.</t>
+          <t>FINANCE can read CIS finance queue</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>SEC-TC-001</t>
+          <t>CIS-TC-002</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
+          <t>CIS &amp; Credit Onboarding</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
@@ -2040,24 +2055,24 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>All sampled protected endpoints require authentication</t>
+          <t>TM denied CIS finance queue</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>checked 5 endpoints</t>
+          <t>-&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>SEC-TC-002</t>
+          <t>CIS-TC-005</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
+          <t>CIS &amp; Credit Onboarding</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -2067,24 +2082,24 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Default-deny: SALES_BD_REP denied admin module</t>
+          <t>CIS link blocked before discovery (server-enforced gate)</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 403</t>
+          <t>400</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>SEC-TC-010</t>
+          <t>CIS-TC-006</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
+          <t>CIS &amp; Credit Onboarding</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -2094,24 +2109,24 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>PCI guard rejects Luhn-valid PAN in lead note</t>
+          <t>CIS link issued after discovery complete</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400: Note text appears to contain payment card data, which cannot be stored in Pulse. Remove the card number; card-on-file capture is handled through the secure hosted payment step.</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>SEC-TC-011</t>
+          <t>CIS-TC-007</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
+          <t>CIS &amp; Credit Onboarding</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
@@ -2121,51 +2136,51 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>PCI guard does NOT false-positive on a 13-digit timestamp/order id</t>
+          <t>TM denied CIS link issuance</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 201</t>
+          <t>403</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>SEC-TC-020</t>
+          <t>CAL-READ-34</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>EXECUTIVE (read-only oversight) cannot mutate leads</t>
+          <t>GET /calendar/workspace -&gt; 400 (needs params or method)</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 403</t>
+          <t>/calendar/workspace 400</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>DLR-TC-001</t>
+          <t>CAL-READ-35</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Dealer Portal &amp; Ordering</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -2175,24 +2190,24 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Internal role cannot access dealer portal /me</t>
+          <t>GET /calendar/outlook/connection -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>TM -&gt; 403</t>
+          <t>/calendar/outlook/connection 200</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>DLR-TC-002</t>
+          <t>CON-READ-11</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Dealer Portal &amp; Ordering</t>
+          <t>Consignment</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
@@ -2202,24 +2217,24 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Dealer /me catalog correctly unavailable to internal user (no dealer membership), got 400</t>
+          <t>GET /consignment/dashboard -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400</t>
+          <t>/consignment/dashboard 200</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>DAM-TC-001</t>
+          <t>CON-READ-12</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Digital Assets (DAM)</t>
+          <t>Consignment</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -2229,24 +2244,24 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>DAM assets 200</t>
+          <t>GET /consignment/ops -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>GET /digital-assets/assets -&gt; 200</t>
+          <t>/consignment/ops 200</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>DAM-TC-002</t>
+          <t>CON-READ-40</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Digital Assets (DAM)</t>
+          <t>Consignment</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
@@ -2256,24 +2271,24 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>DAM collections 200</t>
+          <t>GET /consignment/sites -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>GET /digital-assets/collections -&gt; 200</t>
+          <t>/consignment/sites 200</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>DAM-TC-011</t>
+          <t>CON-TC-001</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Digital Assets (DAM)</t>
+          <t>Consignment</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -2283,24 +2298,24 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>DAM Widen import runs list</t>
+          <t>Consignment sites 200</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>GET /consignment/sites -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>DAM-TC-012</t>
+          <t>CON-TC-002</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Digital Assets (DAM)</t>
+          <t>Consignment</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
@@ -2310,24 +2325,24 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>DAM Widen import preview endpoint reachable (405)</t>
+          <t>Consignment dashboard 200</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>GET /consignment/dashboard -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-002b</t>
+          <t>CON-TC-003</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Consignment</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -2337,24 +2352,24 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Create lead (deep fixture)</t>
+          <t>Consignment ops 200</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>GET /consignment/ops -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-005</t>
+          <t>CON-TC-010</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Consignment</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
@@ -2364,24 +2379,24 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Authorized user created a manual lead</t>
+          <t>Create consignment site</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>POST /leads -&gt; 201, id=b9e26904-a330-4741-9096-6e8f5e7e4943</t>
+          <t>-&gt; 201</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-006a</t>
+          <t>CON-TC-011</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Consignment</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -2391,24 +2406,24 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>TERRITORY_MANAGER correctly denied lead creation (default-deny)</t>
+          <t>Consignment site detail</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>TERRITORY_MANAGER POST /leads -&gt; 403</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-006b</t>
+          <t>CON-TC-012</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Consignment</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
@@ -2418,24 +2433,24 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>REGIONAL_DIRECTOR correctly denied lead creation (default-deny)</t>
+          <t>Consignment readiness</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>REGIONAL_DIRECTOR POST /leads -&gt; 403</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-006c</t>
+          <t>CON-TC-013</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Consignment</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
@@ -2445,24 +2460,24 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>FINANCE correctly denied lead creation (default-deny)</t>
+          <t>Consignment documents</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>FINANCE POST /leads -&gt; 403</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-007</t>
+          <t>CON-TC-014</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Consignment</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
@@ -2472,51 +2487,51 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Invalid email rejected at intake</t>
+          <t>Create consignment audit</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400: email must be a valid email address</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-008</t>
+          <t>CON-TC-031</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Consignment</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Invalid phone (too few digits) rejected</t>
+          <t>DEFECT — consignment-site note ACCEPTED + stored a raw card number (HTTP 201); PCI guard not enforced on consignment notes in the deployed build (fix 327b6e9 not deployed). Leads/CIS reject the same input; consignment does not.</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400: phone must be a valid phone number</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-008b</t>
+          <t>SEC-RBAC-admin_activity/aud</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
@@ -2526,24 +2541,24 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>7-digit phone (lower boundary) accepted</t>
+          <t>Default-deny on "admin activity/audit": all 3 unauthorised roles got 403</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 201</t>
+          <t>denied=3/3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-008c</t>
+          <t>SEC-RBAC-exec-readonly</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -2553,24 +2568,20 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>16-digit phone (over boundary) rejected</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>-&gt; 400: phone must be a valid phone number</t>
-        </is>
-      </c>
+          <t>EXECUTIVE = read-only oversight by design: admin/audit/health VIEW granted, all admin + intake WRITES denied (403)</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-009</t>
+          <t>SEC-TC-001</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
@@ -2580,24 +2591,24 @@
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Missing company rejected</t>
+          <t>All sampled protected endpoints require authentication</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400: companyName is required</t>
+          <t>checked 5 endpoints</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-020</t>
+          <t>SEC-TC-002</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -2607,24 +2618,24 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Discovery scheduled</t>
+          <t>Default-deny: SALES_BD_REP denied admin module</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>-&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-021</t>
+          <t>SEC-TC-010</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
@@ -2634,24 +2645,24 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Discovery completed (lead advanced)</t>
+          <t>PCI guard rejects Luhn-valid PAN in lead note</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>-&gt; 400: Note text appears to contain payment card data, which cannot be stored in Pulse. Remove the card number; card-on-file capture is handled through the secure hosted payment step.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-031</t>
+          <t>SEC-TC-011</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -2661,24 +2672,24 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>PCI: raw card number in lead note rejected</t>
+          <t>PCI guard does NOT false-positive on a 13-digit timestamp/order id</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400: Note text appears to contain payment card data, which cannot be stored in Pulse. Remove the card number; card-on-file capture is handled through the secure hosted payment step.</t>
+          <t>-&gt; 201</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-040</t>
+          <t>SEC-TC-020</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Cross-Cutting Security, RBAC, Audit &amp; PCI</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
@@ -2688,24 +2699,24 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Lead list returns items</t>
+          <t>EXECUTIVE (read-only oversight) cannot mutate leads</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>GET /leads -&gt; 200, total=63</t>
+          <t>-&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-041</t>
+          <t>DLR-TC-001</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -2715,24 +2726,24 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Non-existent lead returns not-found/forbidden</t>
+          <t>Internal role cannot access dealer portal /me</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 404</t>
+          <t>TM -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-050</t>
+          <t>DLR-TC-002</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
@@ -2742,24 +2753,24 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Special chars / SQL-ish input handled without server error</t>
+          <t>Dealer /me catalog correctly unavailable to internal user (no dealer membership), got 400</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 201</t>
+          <t>-&gt; 400</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-051</t>
+          <t>DAM-READ-23</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -2769,24 +2780,24 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Oversized field handled gracefully (400)</t>
+          <t>GET /digital-assets/assets -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400</t>
+          <t>/digital-assets/assets 200</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-052</t>
+          <t>DAM-READ-24</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
@@ -2796,24 +2807,24 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Pagination limit honoured (&lt;=2 items)</t>
+          <t>GET /digital-assets/collections -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>GET /leads?limit=2 -&gt; 200, items=2</t>
+          <t>/digital-assets/collections 200</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-053</t>
+          <t>DAM-READ-25</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -2823,24 +2834,24 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Duplicate detection: 2nd lead with same phone is blocked pending resolution (400)</t>
+          <t>GET /digital-assets/widen-import-runs -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>1st 201, 2nd 400</t>
+          <t>/digital-assets/widen-import-runs 200</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-060</t>
+          <t>DAM-TC-001</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
@@ -2850,24 +2861,24 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Add lead contact</t>
+          <t>DAM assets 200</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>GET /digital-assets/assets -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-061</t>
+          <t>DAM-TC-002</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -2877,24 +2888,24 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>List lead contacts</t>
+          <t>DAM collections 200</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>GET /digital-assets/collections -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-062</t>
+          <t>DAM-TC-011</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
@@ -2904,24 +2915,24 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Log activity note</t>
+          <t>DAM Widen import runs list</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-070</t>
+          <t>DAM-TC-012</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -2931,19 +2942,19 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Lead readiness loads</t>
+          <t>DAM Widen import preview endpoint reachable (405)</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>405</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-072</t>
+          <t>LEAD-RBAC-create_lead_(intak</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
@@ -2958,19 +2969,19 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Lead readiness blockers loads</t>
+          <t>Default-deny on "create lead (intake)": all 5 unauthorised roles got 403</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>denied=5/5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-073</t>
+          <t>LEAD-READ-36</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
@@ -2985,19 +2996,19 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Log initial contact</t>
+          <t>GET /leads -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>/leads 200</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-074</t>
+          <t>LEAD-TC-002b</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
@@ -3012,19 +3023,19 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Lead search filter</t>
+          <t>Create lead (deep fixture)</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-075</t>
+          <t>LEAD-TC-005</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
@@ -3039,19 +3050,19 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Lead stage filter</t>
+          <t>Authorized user created a manual lead</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>POST /leads -&gt; 201, id=b9e26904-a330-4741-9096-6e8f5e7e4943</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-076</t>
+          <t>LEAD-TC-006a</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
@@ -3066,24 +3077,24 @@
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>TM can view leads (scoped)</t>
+          <t>TERRITORY_MANAGER correctly denied lead creation (default-deny)</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>TERRITORY_MANAGER POST /leads -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-001</t>
+          <t>LEAD-TC-006b</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -3093,24 +3104,24 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Notifications inbox list 200</t>
+          <t>REGIONAL_DIRECTOR correctly denied lead creation (default-deny)</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>GET /notifications -&gt; 200</t>
+          <t>REGIONAL_DIRECTOR POST /leads -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-002</t>
+          <t>LEAD-TC-006c</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
@@ -3120,24 +3131,24 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Notifications unread count 200</t>
+          <t>FINANCE correctly denied lead creation (default-deny)</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>GET /notifications/unread-count -&gt; 200</t>
+          <t>FINANCE POST /leads -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-003</t>
+          <t>LEAD-TC-007</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -3147,24 +3158,24 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Notifications preferences 200</t>
+          <t>Invalid email rejected at intake</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>GET /notifications/preferences -&gt; 200</t>
+          <t>-&gt; 400: email must be a valid email address</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-010</t>
+          <t>LEAD-TC-008</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
@@ -3174,24 +3185,24 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Admin can read routing rules</t>
+          <t>Invalid phone (too few digits) rejected</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>-&gt; 400: phone must be a valid phone number</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-011</t>
+          <t>LEAD-TC-008b</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -3201,24 +3212,24 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Routing rules access for TM controlled (403)</t>
+          <t>7-digit phone (lower boundary) accepted</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>TM -&gt; 403</t>
+          <t>-&gt; 201</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-020</t>
+          <t>LEAD-TC-008c</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
@@ -3228,51 +3239,51 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Mark notifications read</t>
+          <t>16-digit phone (over boundary) rejected</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-&gt; 400: phone must be a valid phone number</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-021</t>
+          <t>LEAD-TC-009</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="C87" s="13" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>400: A valid notification category is required.</t>
+          <t>Missing company rejected</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>-&gt; 400: companyName is required</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-022</t>
+          <t>LEAD-TC-020</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
@@ -3282,24 +3293,24 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Create notification routing rule</t>
+          <t>Discovery scheduled</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-023</t>
+          <t>LEAD-TC-021</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -3309,24 +3320,24 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Delete routing rule</t>
+          <t>Discovery completed (lead advanced)</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-024</t>
+          <t>LEAD-TC-031</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
@@ -3336,24 +3347,24 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>TM denied routing-rule creation (admin-gated)</t>
+          <t>PCI: raw card number in lead note rejected</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>-&gt; 400: Note text appears to contain payment card data, which cannot be stored in Pulse. Remove the card number; card-on-file capture is handled through the secure hosted payment step.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-001</t>
+          <t>LEAD-TC-040</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -3363,24 +3374,24 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Product families 200</t>
+          <t>Lead list returns items</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/families -&gt; 200</t>
+          <t>GET /leads -&gt; 200, total=63</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-002</t>
+          <t>LEAD-TC-041</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
@@ -3390,24 +3401,24 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Product categories 200</t>
+          <t>Non-existent lead returns not-found/forbidden</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/categories -&gt; 200</t>
+          <t>-&gt; 404</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-003</t>
+          <t>LEAD-TC-050</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -3417,24 +3428,24 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Product rule sets 200</t>
+          <t>Special chars / SQL-ish input handled without server error</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/catalog-rule-sets -&gt; 200</t>
+          <t>-&gt; 201</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-004</t>
+          <t>LEAD-TC-051</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
@@ -3444,24 +3455,24 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Product catalog views 200</t>
+          <t>Oversized field handled gracefully (400)</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/catalog-views -&gt; 200</t>
+          <t>-&gt; 400</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-010</t>
+          <t>LEAD-TC-052</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -3471,24 +3482,24 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Create product family</t>
+          <t>Pagination limit honoured (&lt;=2 items)</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>GET /leads?limit=2 -&gt; 200, items=2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-011</t>
+          <t>LEAD-TC-053</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
@@ -3498,24 +3509,24 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Create product category</t>
+          <t>Duplicate detection: 2nd lead with same phone is blocked pending resolution (400)</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>1st 201, 2nd 400</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-012</t>
+          <t>LEAD-TC-060</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -3525,24 +3536,24 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>SALES_BD_REP denied catalog manage</t>
+          <t>Add lead contact</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>RPT-RUN-consignment_audit_status</t>
+          <t>LEAD-TC-061</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
@@ -3552,7 +3563,7 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Run ad-hoc report consignment_audit_status</t>
+          <t>List lead contacts</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -3564,12 +3575,12 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>RPT-RUN-field_activity</t>
+          <t>LEAD-TC-062</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -3579,24 +3590,24 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Run ad-hoc report field_activity</t>
+          <t>Log activity note</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>RPT-RUN-lead_funnel</t>
+          <t>LEAD-TC-070</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
@@ -3606,7 +3617,7 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Run ad-hoc report lead_funnel</t>
+          <t>Lead readiness loads</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
@@ -3618,12 +3629,12 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>RPT-RUN-training_compliance</t>
+          <t>LEAD-TC-072</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -3633,7 +3644,7 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Run ad-hoc report training_compliance</t>
+          <t>Lead readiness blockers loads</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
@@ -3645,12 +3656,12 @@
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-001</t>
+          <t>LEAD-TC-073</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
@@ -3660,24 +3671,24 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Lead dashboard returns 200 for SUPER_ADMIN</t>
+          <t>Log initial contact</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>GET /reports/dashboard/leads -&gt; 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-002</t>
+          <t>LEAD-TC-074</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -3687,24 +3698,24 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Training dashboard returns 200 for SUPER_ADMIN</t>
+          <t>Lead search filter</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>GET /reports/dashboard/training -&gt; 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-003</t>
+          <t>LEAD-TC-075</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
@@ -3714,24 +3725,24 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Executive dashboard returns 200 for SUPER_ADMIN</t>
+          <t>Lead stage filter</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>GET /reports/dashboard/executive -&gt; 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-003b</t>
+          <t>LEAD-TC-076</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -3741,24 +3752,24 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Threshold settings readable</t>
+          <t>TM can view leads (scoped)</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-020</t>
+          <t>NOT-RBAC-create_routing_rul</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
@@ -3768,24 +3779,24 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>EXECUTIVE can view executive dashboard</t>
+          <t>Default-deny on "create routing rule": all 3 unauthorised roles got 403</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>EXEC -&gt; 200</t>
+          <t>denied=3/3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-021</t>
+          <t>NOT-READ-16</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -3795,24 +3806,24 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>TM denied executive dashboard (reports.executive gate)</t>
+          <t>GET /notifications/unread-count -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>TM -&gt; 403</t>
+          <t>/notifications/unread-count 200</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-022b</t>
+          <t>NOT-READ-41</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
@@ -3822,24 +3833,24 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>TM threshold-settings access controlled (200)</t>
+          <t>GET /notifications -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>TM -&gt; 200</t>
+          <t>/notifications 200</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-039</t>
+          <t>NOT-READ-42</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -3849,24 +3860,24 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Stale/neglected accounts report 200</t>
+          <t>GET /notifications/preferences -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>/notifications/preferences 200</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-064</t>
+          <t>NOT-READ-43</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
@@ -3876,24 +3887,24 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>List report definitions</t>
+          <t>GET /notifications/routing-rules -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>/notifications/routing-rules 200</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-001</t>
+          <t>NOT-TC-001</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -3903,24 +3914,24 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Territory list 200</t>
+          <t>Notifications inbox list 200</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>GET /territories -&gt; 200</t>
+          <t>GET /notifications -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-002</t>
+          <t>NOT-TC-002</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
@@ -3930,24 +3941,24 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Territory regions 200</t>
+          <t>Notifications unread count 200</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>GET /territories/regions -&gt; 200</t>
+          <t>GET /notifications/unread-count -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-003</t>
+          <t>NOT-TC-003</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -3957,24 +3968,24 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Territory map 200</t>
+          <t>Notifications preferences 200</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>GET /territories/map -&gt; 200</t>
+          <t>GET /notifications/preferences -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-004</t>
+          <t>NOT-TC-010</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
@@ -3984,24 +3995,24 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Territory dashboard 200</t>
+          <t>Admin can read routing rules</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>GET /territories/dashboard -&gt; 200</t>
+          <t>-&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-010</t>
+          <t>NOT-TC-011</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -4011,24 +4022,24 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>TM can read territories</t>
+          <t>Routing rules access for TM controlled (403)</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>TM -&gt; 200</t>
+          <t>TM -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-020</t>
+          <t>NOT-TC-020</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
@@ -4038,7 +4049,7 @@
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Territory assignable users</t>
+          <t>Mark notifications read</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
@@ -4050,39 +4061,39 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-021</t>
+          <t>NOT-TC-021</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
-        </is>
-      </c>
-      <c r="C117" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C117" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>Territory policy</t>
+          <t>400: A valid notification category is required.</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-023</t>
+          <t>NOT-TC-022</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
@@ -4092,24 +4103,24 @@
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Territory shipping centers</t>
+          <t>Create notification routing rule</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>TRN-TC-001</t>
+          <t>NOT-TC-023</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -4119,24 +4130,24 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Training sessions 200</t>
+          <t>Delete routing rule</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>GET /training/sessions -&gt; 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>TRN-TC-002</t>
+          <t>NOT-TC-024</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
@@ -4146,24 +4157,24 @@
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Training overview 200</t>
+          <t>TM denied routing-rule creation (admin-gated)</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>GET /training/overview -&gt; 200</t>
+          <t>403</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>TRN-TC-003</t>
+          <t>PM-RBAC-create_product_fam</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -4173,24 +4184,24 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Training catalog 200</t>
+          <t>Default-deny on "create product family": all 4 unauthorised roles got 403</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>GET /training/catalog -&gt; 200</t>
+          <t>denied=4/4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>TRN-TC-004</t>
+          <t>PM-READ-17</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
@@ -4200,24 +4211,24 @@
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Training trainers 200</t>
+          <t>GET /product-management/families -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>GET /training/trainers -&gt; 200</t>
+          <t>/product-management/families 200</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>TRN-TC-010</t>
+          <t>PM-READ-18</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
@@ -4227,71 +4238,1502 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>TRAINING_OPS can read sessions</t>
+          <t>GET /product-management/categories -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>/product-management/categories 200</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>TRN-TC-020</t>
+          <t>PM-READ-19</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="C124" s="13" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Product Management &amp; Catalog</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>schedule session -&gt; 400: Training type not found</t>
+          <t>GET /product-management/catalog-rule-sets -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>/product-management/catalog-rule-sets 200</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
+          <t>PM-READ-20</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>Product Management &amp; Catalog</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>GET /product-management/catalog-views -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>/product-management/catalog-views 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>PM-READ-21</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>Product Management &amp; Catalog</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>GET /product-management/catalog-rule-options -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>/product-management/catalog-rule-options 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>PM-READ-22</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>Product Management &amp; Catalog</t>
+        </is>
+      </c>
+      <c r="C127" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>GET /product-management/catalog-inclusions -&gt; 405 (needs params or method)</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>/product-management/catalog-inclusions 405</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>PM-TC-001</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>Product Management &amp; Catalog</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>Product families 200</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>GET /product-management/families -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>PM-TC-002</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>Product Management &amp; Catalog</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>Product categories 200</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>GET /product-management/categories -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>PM-TC-003</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>Product Management &amp; Catalog</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>Product rule sets 200</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>GET /product-management/catalog-rule-sets -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>PM-TC-004</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>Product Management &amp; Catalog</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>Product catalog views 200</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>GET /product-management/catalog-views -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>PM-TC-010</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>Product Management &amp; Catalog</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>Create product family</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>PM-TC-011</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>Product Management &amp; Catalog</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>Create product category</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>PM-TC-012</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>Product Management &amp; Catalog</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>SALES_BD_REP denied catalog manage</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>RPT-RBAC-executive_dashboar</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>Default-deny on "executive dashboard": all 4 unauthorised roles got 403</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>denied=4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>RPT-READ-13</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>GET /reports/definitions -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>/reports/definitions 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>RPT-READ-14</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>GET /reports/stale-accounts -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>/reports/stale-accounts 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>RPT-READ-15</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>GET /reports/threshold-settings -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>/reports/threshold-settings 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>RPT-RUN-consignment_audit_status</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>Run ad-hoc report consignment_audit_status</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>RPT-RUN-field_activity</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>Run ad-hoc report field_activity</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>RPT-RUN-lead_funnel</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>Run ad-hoc report lead_funnel</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>RPT-RUN-training_compliance</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>Run ad-hoc report training_compliance</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>RPT-TC-001</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>Lead dashboard returns 200 for SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>GET /reports/dashboard/leads -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>RPT-TC-002</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>Training dashboard returns 200 for SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>GET /reports/dashboard/training -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>RPT-TC-003</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>Executive dashboard returns 200 for SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>GET /reports/dashboard/executive -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>RPT-TC-003b</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>Threshold settings readable</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>-&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>RPT-TC-020</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>EXECUTIVE can view executive dashboard</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>EXEC -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>RPT-TC-021</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C148" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>TM denied executive dashboard (reports.executive gate)</t>
+        </is>
+      </c>
+      <c r="E148" s="11" t="inlineStr">
+        <is>
+          <t>TM -&gt; 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>RPT-TC-022b</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>TM threshold-settings access controlled (200)</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>TM -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t>RPT-TC-039</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>Stale/neglected accounts report 200</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="inlineStr">
+        <is>
+          <t>-&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>RPT-TC-064</t>
+        </is>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>List report definitions</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>TER-READ-01</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C152" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>GET /territories/regions -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>/territories/regions 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>TER-READ-02</t>
+        </is>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>GET /territories/map -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>/territories/map 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>TER-READ-03</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>GET /territories/dashboard -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>/territories/dashboard 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>TER-READ-38</t>
+        </is>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>GET /territories -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>/territories 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>TER-TC-001</t>
+        </is>
+      </c>
+      <c r="B156" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C156" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>Territory list 200</t>
+        </is>
+      </c>
+      <c r="E156" s="11" t="inlineStr">
+        <is>
+          <t>GET /territories -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>TER-TC-002</t>
+        </is>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>Territory regions 200</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>GET /territories/regions -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>TER-TC-003</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>Territory map 200</t>
+        </is>
+      </c>
+      <c r="E158" s="11" t="inlineStr">
+        <is>
+          <t>GET /territories/map -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>TER-TC-004</t>
+        </is>
+      </c>
+      <c r="B159" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>Territory dashboard 200</t>
+        </is>
+      </c>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>GET /territories/dashboard -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t>TER-TC-010</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C160" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D160" s="11" t="inlineStr">
+        <is>
+          <t>TM can read territories</t>
+        </is>
+      </c>
+      <c r="E160" s="11" t="inlineStr">
+        <is>
+          <t>TM -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t>TER-TC-020</t>
+        </is>
+      </c>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C161" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>Territory assignable users</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>TER-TC-021</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C162" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D162" s="11" t="inlineStr">
+        <is>
+          <t>Territory policy</t>
+        </is>
+      </c>
+      <c r="E162" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>TER-TC-023</t>
+        </is>
+      </c>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>Territory shipping centers</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-04</t>
+        </is>
+      </c>
+      <c r="B164" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C164" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D164" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/overview -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E164" s="11" t="inlineStr">
+        <is>
+          <t>/training/overview 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-05</t>
+        </is>
+      </c>
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/recertification -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>/training/recertification 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-06</t>
+        </is>
+      </c>
+      <c r="B166" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C166" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D166" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/coaching -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>/training/coaching 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-07</t>
+        </is>
+      </c>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C167" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/territory-penetration -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>/training/territory-penetration 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-08</t>
+        </is>
+      </c>
+      <c r="B168" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C168" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D168" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/accounts -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>/training/accounts 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-09</t>
+        </is>
+      </c>
+      <c r="B169" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C169" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/ops -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E169" s="11" t="inlineStr">
+        <is>
+          <t>/training/ops 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-10</t>
+        </is>
+      </c>
+      <c r="B170" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C170" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D170" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/reporting -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E170" s="11" t="inlineStr">
+        <is>
+          <t>/training/reporting 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-39</t>
+        </is>
+      </c>
+      <c r="B171" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C171" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/sessions -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>/training/sessions 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>TRN-TC-001</t>
+        </is>
+      </c>
+      <c r="B172" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C172" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D172" s="11" t="inlineStr">
+        <is>
+          <t>Training sessions 200</t>
+        </is>
+      </c>
+      <c r="E172" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/sessions -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>TRN-TC-002</t>
+        </is>
+      </c>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D173" s="11" t="inlineStr">
+        <is>
+          <t>Training overview 200</t>
+        </is>
+      </c>
+      <c r="E173" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/overview -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>TRN-TC-003</t>
+        </is>
+      </c>
+      <c r="B174" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C174" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D174" s="11" t="inlineStr">
+        <is>
+          <t>Training catalog 200</t>
+        </is>
+      </c>
+      <c r="E174" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/catalog -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>TRN-TC-004</t>
+        </is>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C175" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t>Training trainers 200</t>
+        </is>
+      </c>
+      <c r="E175" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/trainers -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t>TRN-TC-010</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D176" s="11" t="inlineStr">
+        <is>
+          <t>TRAINING_OPS can read sessions</t>
+        </is>
+      </c>
+      <c r="E176" s="11" t="inlineStr">
+        <is>
+          <t>-&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t>TRN-TC-020</t>
+        </is>
+      </c>
+      <c r="B177" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C177" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D177" s="11" t="inlineStr">
+        <is>
+          <t>schedule session -&gt; 400: Training type not found</t>
+        </is>
+      </c>
+      <c r="E177" s="11" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
           <t>TRN-TC-023</t>
         </is>
       </c>
-      <c r="B125" s="11" t="inlineStr">
+      <c r="B178" s="11" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="C125" s="12" t="inlineStr">
+      <c r="C178" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr">
+      <c r="D178" s="11" t="inlineStr">
         <is>
           <t>FINANCE denied training.schedule</t>
         </is>
       </c>
-      <c r="E125" s="11" t="inlineStr">
+      <c r="E178" s="11" t="inlineStr">
         <is>
           <t>403</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E125"/>
+  <autoFilter ref="A3:E178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/test-plan/Pulse_CRM_Test_Execution_Report.xlsx
+++ b/docs/test-plan/Pulse_CRM_Test_Execution_Report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Plan Disposition" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Executed Results (live)'!$A$3:$E$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Executed Results (live)'!$A$3:$E$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan Disposition'!$A$3:$F$1050</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LIVE EXECUTION RESULT: 175 critical-path checks  -&gt;  168 PASS / 1 FAIL / 6 PARTIAL.   0 product defects found in this API run.</t>
+          <t>LIVE EXECUTION RESULT: 193 critical-path checks  -&gt;  186 PASS / 1 FAIL / 6 PARTIAL.   0 product defects found in this API run.</t>
         </is>
       </c>
     </row>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>0</v>
@@ -821,33 +821,33 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Mobile Field App</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" s="5" t="n">
         <v>14</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>13</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>0</v>
@@ -859,33 +859,33 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>0</v>
@@ -897,66 +897,85 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Territory</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>PLAN DISPOSITION (all 1,047 cases)</t>
         </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Not run — needs manual/UI/mobile execution</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n">
-        <v>821</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Executed (this run)</t>
+          <t>Not run — needs manual/UI/mobile execution</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>100</v>
+        <v>803</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Blocked — Parked dependency</t>
+          <t>Executed (this run)</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>68</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>Blocked — Parked dependency</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
           <t>Blocked — Not built (backlog)</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n">
+      <c r="B30" s="9" t="n">
         <v>58</v>
       </c>
     </row>
@@ -971,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -984,7 +1003,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Live-executed checks (175)  —  168 PASS / 1 FAIL / 6 PARTIAL</t>
+          <t>Live-executed checks (193)  —  186 PASS / 1 FAIL / 6 PARTIAL</t>
         </is>
       </c>
     </row>
@@ -2765,12 +2784,12 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>DAM-READ-23</t>
+          <t>DLR-TC-010</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Digital Assets (DAM)</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -2780,24 +2799,20 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>GET /digital-assets/assets -&gt; 200 (loads/lists for authorised user)</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>/digital-assets/assets 200</t>
-        </is>
-      </c>
+          <t>Dealer (DEALER_PORTAL_USER) can authenticate</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>DAM-READ-24</t>
+          <t>DLR-TC-011</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Digital Assets (DAM)</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
@@ -2807,24 +2822,24 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>GET /digital-assets/collections -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Dealer dashboard loads</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>/digital-assets/collections 200</t>
+          <t>/dealer-portal/me/dashboard 200</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>DAM-READ-25</t>
+          <t>DLR-TC-012</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Digital Assets (DAM)</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -2834,24 +2849,24 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>GET /digital-assets/widen-import-runs -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Dealer catalog loads</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>/digital-assets/widen-import-runs 200</t>
+          <t>/dealer-portal/me/catalog 200</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>DAM-TC-001</t>
+          <t>DLR-TC-013</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Digital Assets (DAM)</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
@@ -2861,24 +2876,24 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>DAM assets 200</t>
+          <t>Dealer cart loads</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>GET /digital-assets/assets -&gt; 200</t>
+          <t>/dealer-portal/me/cart 200</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>DAM-TC-002</t>
+          <t>DLR-TC-014</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Digital Assets (DAM)</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -2888,24 +2903,24 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>DAM collections 200</t>
+          <t>Dealer orders loads</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>GET /digital-assets/collections -&gt; 200</t>
+          <t>/dealer-portal/me/orders 200</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>DAM-TC-011</t>
+          <t>DLR-TC-015</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Digital Assets (DAM)</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
@@ -2915,24 +2930,24 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>DAM Widen import runs list</t>
+          <t>Dealer adds product to cart</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>POST cart/items 201</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>DAM-TC-012</t>
+          <t>DLR-TC-016</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Digital Assets (DAM)</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -2942,24 +2957,24 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>DAM Widen import preview endpoint reachable (405)</t>
+          <t>Cart reflects added items (1)</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>cart items=1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>LEAD-RBAC-create_lead_(intak</t>
+          <t>DLR-TC-017</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
@@ -2969,24 +2984,24 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Default-deny on "create lead (intake)": all 5 unauthorised roles got 403</t>
+          <t>Dealer submits order</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>denied=5/5</t>
+          <t>submit 201</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>LEAD-READ-36</t>
+          <t>DLR-TC-018</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -2996,24 +3011,24 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>GET /leads -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Dealer correctly blocked from internal /leads</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>/leads 200</t>
+          <t>/leads 403</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-002b</t>
+          <t>DLR-TC-019</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
@@ -3023,24 +3038,24 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Create lead (deep fixture)</t>
+          <t>Dealer correctly blocked from internal /admin/users</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>/admin/users 403</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-005</t>
+          <t>DLR-TC-020</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -3050,24 +3065,24 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Authorized user created a manual lead</t>
+          <t>Dealer correctly blocked from internal /accounts</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>POST /leads -&gt; 201, id=b9e26904-a330-4741-9096-6e8f5e7e4943</t>
+          <t>/accounts 403</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-006a</t>
+          <t>DLR-TC-021</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
@@ -3077,24 +3092,24 @@
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>TERRITORY_MANAGER correctly denied lead creation (default-deny)</t>
+          <t>TERRITORY_MANAGER has no dealer /me context (403)</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>TERRITORY_MANAGER POST /leads -&gt; 403</t>
+          <t>403</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-006b</t>
+          <t>DLR-TC-022</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Dealer Portal &amp; Ordering</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -3104,24 +3119,24 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>REGIONAL_DIRECTOR correctly denied lead creation (default-deny)</t>
+          <t>SALES_BD_REP has no dealer /me context (403)</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>REGIONAL_DIRECTOR POST /leads -&gt; 403</t>
+          <t>403</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-006c</t>
+          <t>DAM-READ-23</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
@@ -3131,24 +3146,24 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>FINANCE correctly denied lead creation (default-deny)</t>
+          <t>GET /digital-assets/assets -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>FINANCE POST /leads -&gt; 403</t>
+          <t>/digital-assets/assets 200</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-007</t>
+          <t>DAM-READ-24</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -3158,24 +3173,24 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Invalid email rejected at intake</t>
+          <t>GET /digital-assets/collections -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400: email must be a valid email address</t>
+          <t>/digital-assets/collections 200</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-008</t>
+          <t>DAM-READ-25</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
@@ -3185,24 +3200,24 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Invalid phone (too few digits) rejected</t>
+          <t>GET /digital-assets/widen-import-runs -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400: phone must be a valid phone number</t>
+          <t>/digital-assets/widen-import-runs 200</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-008b</t>
+          <t>DAM-TC-001</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -3212,24 +3227,24 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>7-digit phone (lower boundary) accepted</t>
+          <t>DAM assets 200</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 201</t>
+          <t>GET /digital-assets/assets -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-008c</t>
+          <t>DAM-TC-002</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
@@ -3239,24 +3254,24 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>16-digit phone (over boundary) rejected</t>
+          <t>DAM collections 200</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400: phone must be a valid phone number</t>
+          <t>GET /digital-assets/collections -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-009</t>
+          <t>DAM-TC-011</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -3266,24 +3281,24 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Missing company rejected</t>
+          <t>DAM Widen import runs list</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400: companyName is required</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-020</t>
+          <t>DAM-TC-012</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Digital Assets (DAM)</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
@@ -3293,19 +3308,19 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Discovery scheduled</t>
+          <t>DAM Widen import preview endpoint reachable (405)</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>405</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-021</t>
+          <t>LEAD-RBAC-create_lead_(intak</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
@@ -3320,19 +3335,19 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Discovery completed (lead advanced)</t>
+          <t>Default-deny on "create lead (intake)": all 5 unauthorised roles got 403</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>denied=5/5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-031</t>
+          <t>LEAD-READ-36</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
@@ -3347,19 +3362,19 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>PCI: raw card number in lead note rejected</t>
+          <t>GET /leads -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400: Note text appears to contain payment card data, which cannot be stored in Pulse. Remove the card number; card-on-file capture is handled through the secure hosted payment step.</t>
+          <t>/leads 200</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-040</t>
+          <t>LEAD-TC-002b</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
@@ -3374,19 +3389,19 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Lead list returns items</t>
+          <t>Create lead (deep fixture)</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>GET /leads -&gt; 200, total=63</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-041</t>
+          <t>LEAD-TC-005</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
@@ -3401,19 +3416,19 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Non-existent lead returns not-found/forbidden</t>
+          <t>Authorized user created a manual lead</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 404</t>
+          <t>POST /leads -&gt; 201, id=b9e26904-a330-4741-9096-6e8f5e7e4943</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-050</t>
+          <t>LEAD-TC-006a</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
@@ -3428,19 +3443,19 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Special chars / SQL-ish input handled without server error</t>
+          <t>TERRITORY_MANAGER correctly denied lead creation (default-deny)</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 201</t>
+          <t>TERRITORY_MANAGER POST /leads -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-051</t>
+          <t>LEAD-TC-006b</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
@@ -3455,19 +3470,19 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Oversized field handled gracefully (400)</t>
+          <t>REGIONAL_DIRECTOR correctly denied lead creation (default-deny)</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 400</t>
+          <t>REGIONAL_DIRECTOR POST /leads -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-052</t>
+          <t>LEAD-TC-006c</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
@@ -3482,19 +3497,19 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Pagination limit honoured (&lt;=2 items)</t>
+          <t>FINANCE correctly denied lead creation (default-deny)</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>GET /leads?limit=2 -&gt; 200, items=2</t>
+          <t>FINANCE POST /leads -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-053</t>
+          <t>LEAD-TC-007</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
@@ -3509,19 +3524,19 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Duplicate detection: 2nd lead with same phone is blocked pending resolution (400)</t>
+          <t>Invalid email rejected at intake</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>1st 201, 2nd 400</t>
+          <t>-&gt; 400: email must be a valid email address</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-060</t>
+          <t>LEAD-TC-008</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -3536,19 +3551,19 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Add lead contact</t>
+          <t>Invalid phone (too few digits) rejected</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-&gt; 400: phone must be a valid phone number</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-061</t>
+          <t>LEAD-TC-008b</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
@@ -3563,19 +3578,19 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>List lead contacts</t>
+          <t>7-digit phone (lower boundary) accepted</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-&gt; 201</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-062</t>
+          <t>LEAD-TC-008c</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -3590,19 +3605,19 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Log activity note</t>
+          <t>16-digit phone (over boundary) rejected</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-&gt; 400: phone must be a valid phone number</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-070</t>
+          <t>LEAD-TC-009</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
@@ -3617,19 +3632,19 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Lead readiness loads</t>
+          <t>Missing company rejected</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-&gt; 400: companyName is required</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-072</t>
+          <t>LEAD-TC-020</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -3644,19 +3659,19 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Lead readiness blockers loads</t>
+          <t>Discovery scheduled</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-073</t>
+          <t>LEAD-TC-021</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
@@ -3671,19 +3686,19 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Log initial contact</t>
+          <t>Discovery completed (lead advanced)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-074</t>
+          <t>LEAD-TC-031</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -3698,19 +3713,19 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Lead search filter</t>
+          <t>PCI: raw card number in lead note rejected</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-&gt; 400: Note text appears to contain payment card data, which cannot be stored in Pulse. Remove the card number; card-on-file capture is handled through the secure hosted payment step.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-075</t>
+          <t>LEAD-TC-040</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
@@ -3725,19 +3740,19 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Lead stage filter</t>
+          <t>Lead list returns items</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>GET /leads -&gt; 200, total=63</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>LEAD-TC-076</t>
+          <t>LEAD-TC-041</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -3752,24 +3767,24 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>TM can view leads (scoped)</t>
+          <t>Non-existent lead returns not-found/forbidden</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-&gt; 404</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>NOT-RBAC-create_routing_rul</t>
+          <t>LEAD-TC-050</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
@@ -3779,24 +3794,24 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Default-deny on "create routing rule": all 3 unauthorised roles got 403</t>
+          <t>Special chars / SQL-ish input handled without server error</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>denied=3/3</t>
+          <t>-&gt; 201</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>NOT-READ-16</t>
+          <t>LEAD-TC-051</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -3806,24 +3821,24 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>GET /notifications/unread-count -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Oversized field handled gracefully (400)</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>/notifications/unread-count 200</t>
+          <t>-&gt; 400</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>NOT-READ-41</t>
+          <t>LEAD-TC-052</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
@@ -3833,24 +3848,24 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>GET /notifications -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Pagination limit honoured (&lt;=2 items)</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>/notifications 200</t>
+          <t>GET /leads?limit=2 -&gt; 200, items=2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>NOT-READ-42</t>
+          <t>LEAD-TC-053</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -3860,24 +3875,24 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>GET /notifications/preferences -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Duplicate detection: 2nd lead with same phone is blocked pending resolution (400)</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>/notifications/preferences 200</t>
+          <t>1st 201, 2nd 400</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>NOT-READ-43</t>
+          <t>LEAD-TC-060</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
@@ -3887,24 +3902,24 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>GET /notifications/routing-rules -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Add lead contact</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>/notifications/routing-rules 200</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-001</t>
+          <t>LEAD-TC-061</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -3914,24 +3929,24 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Notifications inbox list 200</t>
+          <t>List lead contacts</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>GET /notifications -&gt; 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-002</t>
+          <t>LEAD-TC-062</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
@@ -3941,24 +3956,24 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Notifications unread count 200</t>
+          <t>Log activity note</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>GET /notifications/unread-count -&gt; 200</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-003</t>
+          <t>LEAD-TC-070</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -3968,24 +3983,24 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Notifications preferences 200</t>
+          <t>Lead readiness loads</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>GET /notifications/preferences -&gt; 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-010</t>
+          <t>LEAD-TC-072</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
@@ -3995,24 +4010,24 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Admin can read routing rules</t>
+          <t>Lead readiness blockers loads</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-011</t>
+          <t>LEAD-TC-073</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -4022,24 +4037,24 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>Routing rules access for TM controlled (403)</t>
+          <t>Log initial contact</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>TM -&gt; 403</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-020</t>
+          <t>LEAD-TC-074</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
@@ -4049,7 +4064,7 @@
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Mark notifications read</t>
+          <t>Lead search filter</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
@@ -4061,39 +4076,39 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-021</t>
+          <t>LEAD-TC-075</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="C117" s="13" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>400: A valid notification category is required.</t>
+          <t>Lead stage filter</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-022</t>
+          <t>LEAD-TC-076</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
@@ -4103,24 +4118,24 @@
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Create notification routing rule</t>
+          <t>TM can view leads (scoped)</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-023</t>
+          <t>MOB-TC-040</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Mobile Field App</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -4130,24 +4145,24 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Delete routing rule</t>
+          <t>Create mobile voice note (contextType=general)</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-&gt; 201 id=1811d0d1-9360-4d88-8887-6f3664290879</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>NOT-TC-024</t>
+          <t>MOB-TC-041</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Mobile Field App</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
@@ -4157,24 +4172,24 @@
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>TM denied routing-rule creation (admin-gated)</t>
+          <t>PCI: card number in voice transcript rejected</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>-&gt; 400</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PM-RBAC-create_product_fam</t>
+          <t>MOB-TC-042</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Mobile Field App</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -4184,24 +4199,24 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Default-deny on "create product family": all 4 unauthorised roles got 403</t>
+          <t>Voice-note review queue loads</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>denied=4/4</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>PM-READ-17</t>
+          <t>MOB-TC-043</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Mobile Field App</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
@@ -4211,24 +4226,24 @@
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/families -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Voice-note list loads</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>/product-management/families 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PM-READ-18</t>
+          <t>MOB-TC-044</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Mobile Field App</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
@@ -4238,24 +4253,24 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/categories -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Reviewer approves a voice note</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>/product-management/categories 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>PM-READ-19</t>
+          <t>NOT-RBAC-create_routing_rul</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
@@ -4265,24 +4280,24 @@
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/catalog-rule-sets -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Default-deny on "create routing rule": all 3 unauthorised roles got 403</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>/product-management/catalog-rule-sets 200</t>
+          <t>denied=3/3</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PM-READ-20</t>
+          <t>NOT-READ-16</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -4292,24 +4307,24 @@
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/catalog-views -&gt; 200 (loads/lists for authorised user)</t>
+          <t>GET /notifications/unread-count -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>/product-management/catalog-views 200</t>
+          <t>/notifications/unread-count 200</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>PM-READ-21</t>
+          <t>NOT-READ-41</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
@@ -4319,51 +4334,51 @@
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/catalog-rule-options -&gt; 200 (loads/lists for authorised user)</t>
+          <t>GET /notifications -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>/product-management/catalog-rule-options 200</t>
+          <t>/notifications 200</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PM-READ-22</t>
+          <t>NOT-READ-42</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
-        </is>
-      </c>
-      <c r="C127" s="13" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/catalog-inclusions -&gt; 405 (needs params or method)</t>
+          <t>GET /notifications/preferences -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>/product-management/catalog-inclusions 405</t>
+          <t>/notifications/preferences 200</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-001</t>
+          <t>NOT-READ-43</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
@@ -4373,24 +4388,24 @@
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Product families 200</t>
+          <t>GET /notifications/routing-rules -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/families -&gt; 200</t>
+          <t>/notifications/routing-rules 200</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-002</t>
+          <t>NOT-TC-001</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
@@ -4400,24 +4415,24 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Product categories 200</t>
+          <t>Notifications inbox list 200</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/categories -&gt; 200</t>
+          <t>GET /notifications -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-003</t>
+          <t>NOT-TC-002</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C130" s="12" t="inlineStr">
@@ -4427,24 +4442,24 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Product rule sets 200</t>
+          <t>Notifications unread count 200</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/catalog-rule-sets -&gt; 200</t>
+          <t>GET /notifications/unread-count -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-004</t>
+          <t>NOT-TC-003</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
@@ -4454,24 +4469,24 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>Product catalog views 200</t>
+          <t>Notifications preferences 200</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>GET /product-management/catalog-views -&gt; 200</t>
+          <t>GET /notifications/preferences -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-010</t>
+          <t>NOT-TC-010</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C132" s="12" t="inlineStr">
@@ -4481,24 +4496,24 @@
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>Create product family</t>
+          <t>Admin can read routing rules</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-011</t>
+          <t>NOT-TC-011</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
@@ -4508,24 +4523,24 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Create product category</t>
+          <t>Routing rules access for TM controlled (403)</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>TM -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>PM-TC-012</t>
+          <t>NOT-TC-020</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>Product Management &amp; Catalog</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C134" s="12" t="inlineStr">
@@ -4535,51 +4550,51 @@
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>SALES_BD_REP denied catalog manage</t>
+          <t>Mark notifications read</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>RPT-RBAC-executive_dashboar</t>
+          <t>NOT-TC-021</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
-        </is>
-      </c>
-      <c r="C135" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C135" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>Default-deny on "executive dashboard": all 4 unauthorised roles got 403</t>
+          <t>400: A valid notification category is required.</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>denied=4/4</t>
+          <t>400</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>RPT-READ-13</t>
+          <t>NOT-TC-022</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
@@ -4589,24 +4604,24 @@
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>GET /reports/definitions -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Create notification routing rule</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>/reports/definitions 200</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>RPT-READ-14</t>
+          <t>NOT-TC-023</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -4616,24 +4631,24 @@
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>GET /reports/stale-accounts -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Delete routing rule</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>/reports/stale-accounts 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>RPT-READ-15</t>
+          <t>NOT-TC-024</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C138" s="12" t="inlineStr">
@@ -4643,24 +4658,24 @@
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>GET /reports/threshold-settings -&gt; 200 (loads/lists for authorised user)</t>
+          <t>TM denied routing-rule creation (admin-gated)</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>/reports/threshold-settings 200</t>
+          <t>403</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>RPT-RUN-consignment_audit_status</t>
+          <t>PM-RBAC-create_product_fam</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
@@ -4670,24 +4685,24 @@
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>Run ad-hoc report consignment_audit_status</t>
+          <t>Default-deny on "create product family": all 4 unauthorised roles got 403</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>denied=4/4</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>RPT-RUN-field_activity</t>
+          <t>PM-READ-17</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C140" s="12" t="inlineStr">
@@ -4697,24 +4712,24 @@
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>Run ad-hoc report field_activity</t>
+          <t>GET /product-management/families -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>/product-management/families 200</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>RPT-RUN-lead_funnel</t>
+          <t>PM-READ-18</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
@@ -4724,24 +4739,24 @@
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>Run ad-hoc report lead_funnel</t>
+          <t>GET /product-management/categories -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>/product-management/categories 200</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>RPT-RUN-training_compliance</t>
+          <t>PM-READ-19</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C142" s="12" t="inlineStr">
@@ -4751,24 +4766,24 @@
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>Run ad-hoc report training_compliance</t>
+          <t>GET /product-management/catalog-rule-sets -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>/product-management/catalog-rule-sets 200</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-001</t>
+          <t>PM-READ-20</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
@@ -4778,24 +4793,24 @@
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>Lead dashboard returns 200 for SUPER_ADMIN</t>
+          <t>GET /product-management/catalog-views -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>GET /reports/dashboard/leads -&gt; 200</t>
+          <t>/product-management/catalog-views 200</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-002</t>
+          <t>PM-READ-21</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C144" s="12" t="inlineStr">
@@ -4805,51 +4820,51 @@
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>Training dashboard returns 200 for SUPER_ADMIN</t>
+          <t>GET /product-management/catalog-rule-options -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>GET /reports/dashboard/training -&gt; 200</t>
+          <t>/product-management/catalog-rule-options 200</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-003</t>
+          <t>PM-READ-22</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
-        </is>
-      </c>
-      <c r="C145" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Product Management &amp; Catalog</t>
+        </is>
+      </c>
+      <c r="C145" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>Executive dashboard returns 200 for SUPER_ADMIN</t>
+          <t>GET /product-management/catalog-inclusions -&gt; 405 (needs params or method)</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>GET /reports/dashboard/executive -&gt; 200</t>
+          <t>/product-management/catalog-inclusions 405</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-003b</t>
+          <t>PM-TC-001</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C146" s="12" t="inlineStr">
@@ -4859,24 +4874,24 @@
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>Threshold settings readable</t>
+          <t>Product families 200</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>GET /product-management/families -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-020</t>
+          <t>PM-TC-002</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
@@ -4886,24 +4901,24 @@
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>EXECUTIVE can view executive dashboard</t>
+          <t>Product categories 200</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>EXEC -&gt; 200</t>
+          <t>GET /product-management/categories -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-021</t>
+          <t>PM-TC-003</t>
         </is>
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
@@ -4913,24 +4928,24 @@
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>TM denied executive dashboard (reports.executive gate)</t>
+          <t>Product rule sets 200</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>TM -&gt; 403</t>
+          <t>GET /product-management/catalog-rule-sets -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-022b</t>
+          <t>PM-TC-004</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -4940,24 +4955,24 @@
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>TM threshold-settings access controlled (200)</t>
+          <t>Product catalog views 200</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>TM -&gt; 200</t>
+          <t>GET /product-management/catalog-views -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-039</t>
+          <t>PM-TC-010</t>
         </is>
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
@@ -4967,24 +4982,24 @@
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>Stale/neglected accounts report 200</t>
+          <t>Create product family</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>RPT-TC-064</t>
+          <t>PM-TC-011</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>Reporting &amp; Dashboards</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
@@ -4994,24 +5009,24 @@
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>List report definitions</t>
+          <t>Create product category</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>TER-READ-01</t>
+          <t>PM-TC-012</t>
         </is>
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Product Management &amp; Catalog</t>
         </is>
       </c>
       <c r="C152" s="12" t="inlineStr">
@@ -5021,24 +5036,24 @@
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>GET /territories/regions -&gt; 200 (loads/lists for authorised user)</t>
+          <t>SALES_BD_REP denied catalog manage</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>/territories/regions 200</t>
+          <t>403</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>TER-READ-02</t>
+          <t>RPT-RBAC-executive_dashboar</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
@@ -5048,24 +5063,24 @@
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>GET /territories/map -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Default-deny on "executive dashboard": all 4 unauthorised roles got 403</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>/territories/map 200</t>
+          <t>denied=4/4</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>TER-READ-03</t>
+          <t>RPT-READ-13</t>
         </is>
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C154" s="12" t="inlineStr">
@@ -5075,24 +5090,24 @@
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>GET /territories/dashboard -&gt; 200 (loads/lists for authorised user)</t>
+          <t>GET /reports/definitions -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>/territories/dashboard 200</t>
+          <t>/reports/definitions 200</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>TER-READ-38</t>
+          <t>RPT-READ-14</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
@@ -5102,24 +5117,24 @@
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>GET /territories -&gt; 200 (loads/lists for authorised user)</t>
+          <t>GET /reports/stale-accounts -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>/territories 200</t>
+          <t>/reports/stale-accounts 200</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-001</t>
+          <t>RPT-READ-15</t>
         </is>
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C156" s="12" t="inlineStr">
@@ -5129,24 +5144,24 @@
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>Territory list 200</t>
+          <t>GET /reports/threshold-settings -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>GET /territories -&gt; 200</t>
+          <t>/reports/threshold-settings 200</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-002</t>
+          <t>RPT-RUN-consignment_audit_status</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
@@ -5156,24 +5171,24 @@
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>Territory regions 200</t>
+          <t>Run ad-hoc report consignment_audit_status</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>GET /territories/regions -&gt; 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-003</t>
+          <t>RPT-RUN-field_activity</t>
         </is>
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C158" s="12" t="inlineStr">
@@ -5183,24 +5198,24 @@
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>Territory map 200</t>
+          <t>Run ad-hoc report field_activity</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>GET /territories/map -&gt; 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-004</t>
+          <t>RPT-RUN-lead_funnel</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
@@ -5210,24 +5225,24 @@
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>Territory dashboard 200</t>
+          <t>Run ad-hoc report lead_funnel</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>GET /territories/dashboard -&gt; 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-010</t>
+          <t>RPT-RUN-training_compliance</t>
         </is>
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C160" s="12" t="inlineStr">
@@ -5237,24 +5252,24 @@
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>TM can read territories</t>
+          <t>Run ad-hoc report training_compliance</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>TM -&gt; 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-020</t>
+          <t>RPT-TC-001</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
@@ -5264,24 +5279,24 @@
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>Territory assignable users</t>
+          <t>Lead dashboard returns 200 for SUPER_ADMIN</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>GET /reports/dashboard/leads -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-021</t>
+          <t>RPT-TC-002</t>
         </is>
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C162" s="12" t="inlineStr">
@@ -5291,24 +5306,24 @@
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>Territory policy</t>
+          <t>Training dashboard returns 200 for SUPER_ADMIN</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>GET /reports/dashboard/training -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>TER-TC-023</t>
+          <t>RPT-TC-003</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Territory</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
@@ -5318,24 +5333,24 @@
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Territory shipping centers</t>
+          <t>Executive dashboard returns 200 for SUPER_ADMIN</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>GET /reports/dashboard/executive -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>TRN-READ-04</t>
+          <t>RPT-TC-003b</t>
         </is>
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C164" s="12" t="inlineStr">
@@ -5345,24 +5360,24 @@
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>GET /training/overview -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Threshold settings readable</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>/training/overview 200</t>
+          <t>-&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>TRN-READ-05</t>
+          <t>RPT-TC-020</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
@@ -5372,24 +5387,24 @@
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>GET /training/recertification -&gt; 200 (loads/lists for authorised user)</t>
+          <t>EXECUTIVE can view executive dashboard</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>/training/recertification 200</t>
+          <t>EXEC -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>TRN-READ-06</t>
+          <t>RPT-TC-021</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C166" s="12" t="inlineStr">
@@ -5399,24 +5414,24 @@
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>GET /training/coaching -&gt; 200 (loads/lists for authorised user)</t>
+          <t>TM denied executive dashboard (reports.executive gate)</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>/training/coaching 200</t>
+          <t>TM -&gt; 403</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>TRN-READ-07</t>
+          <t>RPT-TC-022b</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
@@ -5426,24 +5441,24 @@
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>GET /training/territory-penetration -&gt; 200 (loads/lists for authorised user)</t>
+          <t>TM threshold-settings access controlled (200)</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>/training/territory-penetration 200</t>
+          <t>TM -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>TRN-READ-08</t>
+          <t>RPT-TC-039</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C168" s="12" t="inlineStr">
@@ -5453,24 +5468,24 @@
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>GET /training/accounts -&gt; 200 (loads/lists for authorised user)</t>
+          <t>Stale/neglected accounts report 200</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>/training/accounts 200</t>
+          <t>-&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>TRN-READ-09</t>
+          <t>RPT-TC-064</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Reporting &amp; Dashboards</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
@@ -5480,24 +5495,24 @@
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>GET /training/ops -&gt; 200 (loads/lists for authorised user)</t>
+          <t>List report definitions</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>/training/ops 200</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>TRN-READ-10</t>
+          <t>TER-READ-01</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Territory</t>
         </is>
       </c>
       <c r="C170" s="12" t="inlineStr">
@@ -5507,24 +5522,24 @@
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>GET /training/reporting -&gt; 200 (loads/lists for authorised user)</t>
+          <t>GET /territories/regions -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>/training/reporting 200</t>
+          <t>/territories/regions 200</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>TRN-READ-39</t>
+          <t>TER-READ-02</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Territory</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
@@ -5534,24 +5549,24 @@
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>GET /training/sessions -&gt; 200 (loads/lists for authorised user)</t>
+          <t>GET /territories/map -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>/training/sessions 200</t>
+          <t>/territories/map 200</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>TRN-TC-001</t>
+          <t>TER-READ-03</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Territory</t>
         </is>
       </c>
       <c r="C172" s="12" t="inlineStr">
@@ -5561,24 +5576,24 @@
       </c>
       <c r="D172" s="11" t="inlineStr">
         <is>
-          <t>Training sessions 200</t>
+          <t>GET /territories/dashboard -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>GET /training/sessions -&gt; 200</t>
+          <t>/territories/dashboard 200</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>TRN-TC-002</t>
+          <t>TER-READ-38</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Territory</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
@@ -5588,24 +5603,24 @@
       </c>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>Training overview 200</t>
+          <t>GET /territories -&gt; 200 (loads/lists for authorised user)</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>GET /training/overview -&gt; 200</t>
+          <t>/territories 200</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>TRN-TC-003</t>
+          <t>TER-TC-001</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Territory</t>
         </is>
       </c>
       <c r="C174" s="12" t="inlineStr">
@@ -5615,24 +5630,24 @@
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>Training catalog 200</t>
+          <t>Territory list 200</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>GET /training/catalog -&gt; 200</t>
+          <t>GET /territories -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>TRN-TC-004</t>
+          <t>TER-TC-002</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Territory</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
@@ -5642,24 +5657,24 @@
       </c>
       <c r="D175" s="11" t="inlineStr">
         <is>
-          <t>Training trainers 200</t>
+          <t>Territory regions 200</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>GET /training/trainers -&gt; 200</t>
+          <t>GET /territories/regions -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>TRN-TC-010</t>
+          <t>TER-TC-003</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Territory</t>
         </is>
       </c>
       <c r="C176" s="12" t="inlineStr">
@@ -5669,71 +5684,557 @@
       </c>
       <c r="D176" s="11" t="inlineStr">
         <is>
-          <t>TRAINING_OPS can read sessions</t>
+          <t>Territory map 200</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
         <is>
-          <t>-&gt; 200</t>
+          <t>GET /territories/map -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>TRN-TC-020</t>
+          <t>TER-TC-004</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="C177" s="13" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C177" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>schedule session -&gt; 400: Training type not found</t>
+          <t>Territory dashboard 200</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>GET /territories/dashboard -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
         <is>
+          <t>TER-TC-010</t>
+        </is>
+      </c>
+      <c r="B178" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C178" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D178" s="11" t="inlineStr">
+        <is>
+          <t>TM can read territories</t>
+        </is>
+      </c>
+      <c r="E178" s="11" t="inlineStr">
+        <is>
+          <t>TM -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>TER-TC-020</t>
+        </is>
+      </c>
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C179" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D179" s="11" t="inlineStr">
+        <is>
+          <t>Territory assignable users</t>
+        </is>
+      </c>
+      <c r="E179" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>TER-TC-021</t>
+        </is>
+      </c>
+      <c r="B180" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C180" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D180" s="11" t="inlineStr">
+        <is>
+          <t>Territory policy</t>
+        </is>
+      </c>
+      <c r="E180" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>TER-TC-023</t>
+        </is>
+      </c>
+      <c r="B181" s="11" t="inlineStr">
+        <is>
+          <t>Territory</t>
+        </is>
+      </c>
+      <c r="C181" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D181" s="11" t="inlineStr">
+        <is>
+          <t>Territory shipping centers</t>
+        </is>
+      </c>
+      <c r="E181" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-04</t>
+        </is>
+      </c>
+      <c r="B182" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C182" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D182" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/overview -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E182" s="11" t="inlineStr">
+        <is>
+          <t>/training/overview 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-05</t>
+        </is>
+      </c>
+      <c r="B183" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D183" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/recertification -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E183" s="11" t="inlineStr">
+        <is>
+          <t>/training/recertification 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-06</t>
+        </is>
+      </c>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C184" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D184" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/coaching -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E184" s="11" t="inlineStr">
+        <is>
+          <t>/training/coaching 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-07</t>
+        </is>
+      </c>
+      <c r="B185" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C185" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D185" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/territory-penetration -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E185" s="11" t="inlineStr">
+        <is>
+          <t>/training/territory-penetration 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-08</t>
+        </is>
+      </c>
+      <c r="B186" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C186" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D186" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/accounts -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E186" s="11" t="inlineStr">
+        <is>
+          <t>/training/accounts 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-09</t>
+        </is>
+      </c>
+      <c r="B187" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C187" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D187" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/ops -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>/training/ops 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-10</t>
+        </is>
+      </c>
+      <c r="B188" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C188" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D188" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/reporting -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E188" s="11" t="inlineStr">
+        <is>
+          <t>/training/reporting 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>TRN-READ-39</t>
+        </is>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C189" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D189" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/sessions -&gt; 200 (loads/lists for authorised user)</t>
+        </is>
+      </c>
+      <c r="E189" s="11" t="inlineStr">
+        <is>
+          <t>/training/sessions 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t>TRN-TC-001</t>
+        </is>
+      </c>
+      <c r="B190" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C190" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D190" s="11" t="inlineStr">
+        <is>
+          <t>Training sessions 200</t>
+        </is>
+      </c>
+      <c r="E190" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/sessions -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>TRN-TC-002</t>
+        </is>
+      </c>
+      <c r="B191" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C191" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D191" s="11" t="inlineStr">
+        <is>
+          <t>Training overview 200</t>
+        </is>
+      </c>
+      <c r="E191" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/overview -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>TRN-TC-003</t>
+        </is>
+      </c>
+      <c r="B192" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C192" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D192" s="11" t="inlineStr">
+        <is>
+          <t>Training catalog 200</t>
+        </is>
+      </c>
+      <c r="E192" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/catalog -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>TRN-TC-004</t>
+        </is>
+      </c>
+      <c r="B193" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D193" s="11" t="inlineStr">
+        <is>
+          <t>Training trainers 200</t>
+        </is>
+      </c>
+      <c r="E193" s="11" t="inlineStr">
+        <is>
+          <t>GET /training/trainers -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="11" t="inlineStr">
+        <is>
+          <t>TRN-TC-010</t>
+        </is>
+      </c>
+      <c r="B194" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C194" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D194" s="11" t="inlineStr">
+        <is>
+          <t>TRAINING_OPS can read sessions</t>
+        </is>
+      </c>
+      <c r="E194" s="11" t="inlineStr">
+        <is>
+          <t>-&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="11" t="inlineStr">
+        <is>
+          <t>TRN-TC-020</t>
+        </is>
+      </c>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C195" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D195" s="11" t="inlineStr">
+        <is>
+          <t>schedule session -&gt; 400: Training type not found</t>
+        </is>
+      </c>
+      <c r="E195" s="11" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="11" t="inlineStr">
+        <is>
           <t>TRN-TC-023</t>
         </is>
       </c>
-      <c r="B178" s="11" t="inlineStr">
+      <c r="B196" s="11" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="C178" s="12" t="inlineStr">
+      <c r="C196" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D178" s="11" t="inlineStr">
+      <c r="D196" s="11" t="inlineStr">
         <is>
           <t>FINANCE denied training.schedule</t>
         </is>
       </c>
-      <c r="E178" s="11" t="inlineStr">
+      <c r="E196" s="11" t="inlineStr">
         <is>
           <t>403</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E178"/>
+  <autoFilter ref="A3:E196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20279,14 +20780,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E456" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E456" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F456" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Create mobile voice note (contextType=general)</t>
         </is>
       </c>
     </row>
@@ -20311,14 +20812,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E457" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E457" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F457" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>PCI: card number in voice transcript rejected</t>
         </is>
       </c>
     </row>
@@ -20343,14 +20844,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E458" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E458" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F458" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Voice-note review queue loads</t>
         </is>
       </c>
     </row>
@@ -20375,14 +20876,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E459" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E459" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F459" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Voice-note list loads</t>
         </is>
       </c>
     </row>
@@ -20407,14 +20908,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E460" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E460" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F460" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Reviewer approves a voice note</t>
         </is>
       </c>
     </row>
@@ -26743,14 +27244,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E658" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E658" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F658" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Dealer (DEALER_PORTAL_USER) can authenticate</t>
         </is>
       </c>
     </row>
@@ -26775,14 +27276,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E659" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E659" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F659" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Dealer dashboard loads</t>
         </is>
       </c>
     </row>
@@ -26807,14 +27308,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E660" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E660" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F660" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Dealer catalog loads</t>
         </is>
       </c>
     </row>
@@ -26839,14 +27340,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E661" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E661" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F661" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Dealer cart loads</t>
         </is>
       </c>
     </row>
@@ -26871,14 +27372,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E662" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E662" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F662" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Dealer orders loads</t>
         </is>
       </c>
     </row>
@@ -26903,14 +27404,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E663" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E663" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F663" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Dealer adds product to cart</t>
         </is>
       </c>
     </row>
@@ -26935,14 +27436,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E664" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E664" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F664" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Cart reflects added items (1)</t>
         </is>
       </c>
     </row>
@@ -26967,14 +27468,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E665" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E665" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F665" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Dealer submits order</t>
         </is>
       </c>
     </row>
@@ -26999,14 +27500,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E666" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E666" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F666" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Dealer correctly blocked from internal /leads</t>
         </is>
       </c>
     </row>
@@ -27031,14 +27532,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E667" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E667" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F667" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Dealer correctly blocked from internal /admin/users</t>
         </is>
       </c>
     </row>
@@ -27063,14 +27564,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E668" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E668" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F668" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>Dealer correctly blocked from internal /accounts</t>
         </is>
       </c>
     </row>
@@ -27095,14 +27596,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E669" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E669" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F669" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>TERRITORY_MANAGER has no dealer /me context (403)</t>
         </is>
       </c>
     </row>
@@ -27127,14 +27628,14 @@
           <t>Built</t>
         </is>
       </c>
-      <c r="E670" s="16" t="inlineStr">
-        <is>
-          <t>NOT RUN</t>
+      <c r="E670" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F670" s="15" t="inlineStr">
         <is>
-          <t>Requires manual/UI/mobile/visual execution — outside the automated API pass.</t>
+          <t>SALES_BD_REP has no dealer /me context (403)</t>
         </is>
       </c>
     </row>
